--- a/workspace/framework_paper/edf/edf-25/edf-25_times.xlsx
+++ b/workspace/framework_paper/edf/edf-25/edf-25_times.xlsx
@@ -438,13 +438,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01030085004866123</v>
+        <v>0.01080446679145098</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02993443315848708</v>
+        <v>0.0271935884654522</v>
       </c>
       <c r="D2" t="n">
-        <v>7.330829051695764</v>
+        <v>0.01848845755681396</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01146752014756203</v>
+        <v>0.01145003156736493</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03356355478987098</v>
+        <v>0.03204548183828592</v>
       </c>
       <c r="D3" t="n">
-        <v>7.907540046051144</v>
+        <v>0.1616352900024504</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01366270853206515</v>
+        <v>0.01245177505537868</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04094134533777833</v>
+        <v>0.03916463673114776</v>
       </c>
       <c r="D4" t="n">
-        <v>9.524796094074846</v>
+        <v>0.1847511786222458</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01443847822956741</v>
+        <v>0.01407932668924332</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05590956483036279</v>
+        <v>0.05102823821827769</v>
       </c>
       <c r="D5" t="n">
-        <v>29.38367764949799</v>
+        <v>1.137900152858347</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02879136787727475</v>
+        <v>0.02709043679758906</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1041874108463526</v>
+        <v>0.09786016073077917</v>
       </c>
       <c r="D6" t="n">
-        <v>44.55416973590851</v>
+        <v>6.97311979142949</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0179903267044574</v>
+        <v>0.01715131926350295</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4928269763663411</v>
+        <v>0.3933099031075835</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53491545200348</v>
+        <v>1.80423461260274</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02745839825831354</v>
+        <v>0.02556412174366415</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5155694557726384</v>
+        <v>0.4598420738428831</v>
       </c>
       <c r="D8" t="n">
-        <v>59.87739661693573</v>
+        <v>5.48067173037678</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03343783468008042</v>
+        <v>0.03259878627490252</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9958723288029432</v>
+        <v>0.9715954983979463</v>
       </c>
       <c r="D9" t="n">
-        <v>58.46869134902954</v>
+        <v>13.04418313145637</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02321529818698764</v>
+        <v>0.02298102505505085</v>
       </c>
       <c r="C10" t="n">
-        <v>5.166005160585046</v>
+        <v>5.274435861334204</v>
       </c>
       <c r="D10" t="n">
-        <v>135.4923836517334</v>
+        <v>31.61276098027825</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.03171359384432435</v>
+        <v>0.03100047991611064</v>
       </c>
       <c r="C11" t="n">
-        <v>9.235450968816876</v>
+        <v>9.169239283576609</v>
       </c>
       <c r="D11" t="n">
-        <v>160.8401723194122</v>
+        <v>47.04183860652149</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02176243579946458</v>
+        <v>0.02118405253626406</v>
       </c>
       <c r="C12" t="n">
-        <v>21.0762256936729</v>
+        <v>20.48907344192266</v>
       </c>
       <c r="D12" t="n">
-        <v>165.353662443161</v>
+        <v>82.88472431764006</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0269292317237705</v>
+        <v>0.02644419029355049</v>
       </c>
       <c r="C13" t="n">
-        <v>38.90813511177898</v>
+        <v>38.68344816893339</v>
       </c>
       <c r="D13" t="n">
-        <v>213.7440552902222</v>
+        <v>408.8007970053703</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01983232014579699</v>
+        <v>0.01973946243524551</v>
       </c>
       <c r="C14" t="n">
-        <v>36.56956786751747</v>
+        <v>36.01403942584992</v>
       </c>
       <c r="D14" t="n">
-        <v>343.4845182037354</v>
+        <v>176.0190153697878</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01689696842804551</v>
+        <v>0.01653248997405172</v>
       </c>
       <c r="C15" t="n">
-        <v>52.25363228201866</v>
+        <v>51.95326505854726</v>
       </c>
       <c r="D15" t="n">
-        <v>328.7794462585449</v>
+        <v>231.6966193476319</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01591655079741031</v>
+        <v>0.01605420415755361</v>
       </c>
       <c r="C16" t="n">
-        <v>61.0480602440238</v>
+        <v>60.94048849076032</v>
       </c>
       <c r="D16" t="n">
-        <v>489.9315313339233</v>
+        <v>428.5146276579797</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01535864152945578</v>
+        <v>0.01542980663944036</v>
       </c>
       <c r="C17" t="n">
-        <v>67.63009744316339</v>
+        <v>67.79127611309291</v>
       </c>
       <c r="D17" t="n">
-        <v>661.8694378662109</v>
+        <v>566.3731377789378</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01294447410386056</v>
+        <v>0.01350447665667161</v>
       </c>
       <c r="C18" t="n">
-        <v>79.52951059877873</v>
+        <v>78.8303523260355</v>
       </c>
       <c r="D18" t="n">
-        <v>761.9997681808471</v>
+        <v>733.2124031066894</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01544151426060125</v>
+        <v>0.01514816239010543</v>
       </c>
       <c r="C19" t="n">
-        <v>88.98825932025909</v>
+        <v>87.43663558721542</v>
       </c>
       <c r="D19" t="n">
-        <v>931.5933478546143</v>
+        <v>832.5832888793946</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01469059736933559</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>98.03345664978028</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1336.433911437988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">

--- a/workspace/framework_paper/edf/edf-25/edf-25_times.xlsx
+++ b/workspace/framework_paper/edf/edf-25/edf-25_times.xlsx
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01514816239010543</v>
+        <v>0.01349916076520458</v>
       </c>
       <c r="C19" t="n">
-        <v>87.43663558721542</v>
+        <v>84.46699774503708</v>
       </c>
       <c r="D19" t="n">
-        <v>832.5832888793946</v>
+        <v>964.7042343139649</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.01475639497162774</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>108.7584681415558</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1205.477171325684</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.01658967067953199</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>110.8115614700317</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1224.684067382813</v>
       </c>
     </row>
   </sheetData>
